--- a/results/assessment/vIAbility/features/markers/ML/iter1/cv_results.xlsx
+++ b/results/assessment/vIAbility/features/markers/ML/iter1/cv_results.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -558,646 +558,560 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GaussianNB</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4398</v>
+        <v>0.4069</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2993</v>
+        <v>0.2395</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4002</v>
+        <v>0.3521</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3542</v>
+        <v>0.2968</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.466</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0276</v>
+        <v>0.0471</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0611</v>
+        <v>0.0922</v>
       </c>
       <c r="J3" t="n">
-        <v>0.048</v>
+        <v>0.0593</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0502</v>
+        <v>0.0678</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0461</v>
+        <v>0.0568</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0408</v>
+        <v>0.0721</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>GaussianNB</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4307</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3807</v>
+        <v>0.4398</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6866</v>
+        <v>0.2993</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4167</v>
+        <v>0.4002</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4868</v>
+        <v>0.3542</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4758</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0321</v>
+        <v>0.0276</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0391</v>
+        <v>0.0611</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1788</v>
+        <v>0.048</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0512</v>
+        <v>0.0502</v>
       </c>
       <c r="L4" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.0461</v>
       </c>
       <c r="M4" t="n">
-        <v>0.06510000000000001</v>
+        <v>0.0408</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MLPClassifier</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4861</v>
+        <v>0.4307</v>
       </c>
       <c r="C5" t="n">
-        <v>0.4064</v>
+        <v>0.3807</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5547</v>
+        <v>0.6866</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4271</v>
+        <v>0.4167</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4644</v>
+        <v>0.4868</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5222</v>
+        <v>0.4758</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0411</v>
+        <v>0.0321</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0191</v>
+        <v>0.0391</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1007</v>
+        <v>0.1788</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0121</v>
+        <v>0.0512</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0256</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0201</v>
+        <v>0.06510000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LogisticRegression</t>
+          <t>MLPClassifier</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5347</v>
+        <v>0.4861</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4384</v>
+        <v>0.4064</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5138</v>
+        <v>0.5547</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4513</v>
+        <v>0.4271</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4726</v>
+        <v>0.4644</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5304</v>
+        <v>0.5222</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0769</v>
+        <v>0.0411</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0771</v>
+        <v>0.0191</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09810000000000001</v>
+        <v>0.1007</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0794</v>
+        <v>0.0121</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0844</v>
+        <v>0.0256</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0823</v>
+        <v>0.0201</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TabPFN</t>
+          <t>LogisticRegression</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.5799</v>
+        <v>0.5347</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1667</v>
+        <v>0.4384</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0341</v>
+        <v>0.5138</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0926</v>
+        <v>0.4513</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0562</v>
+        <v>0.4726</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5323</v>
+        <v>0.5304</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02</v>
+        <v>0.0769</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2108</v>
+        <v>0.0771</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0417</v>
+        <v>0.09810000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.114</v>
+        <v>0.0794</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0688</v>
+        <v>0.0844</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0769</v>
+        <v>0.0823</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bagging_RandomForest</t>
+          <t>TabPFN</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5347</v>
+        <v>0.5799</v>
       </c>
       <c r="C8" t="n">
-        <v>0.385</v>
+        <v>0.1667</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2149</v>
+        <v>0.0341</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3267</v>
+        <v>0.0926</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2713</v>
+        <v>0.0562</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4657</v>
+        <v>0.5323</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0553</v>
+        <v>0.02</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1084</v>
+        <v>0.2108</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0641</v>
+        <v>0.0417</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0838</v>
+        <v>0.114</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0725</v>
+        <v>0.0688</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0572</v>
+        <v>0.0769</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bagging_SVC</t>
+          <t>Bagging_RandomForest</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.5347</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4536</v>
+        <v>0.385</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2384</v>
+        <v>0.2149</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3782</v>
+        <v>0.3267</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3075</v>
+        <v>0.2713</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5082</v>
+        <v>0.4657</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0747</v>
+        <v>0.0553</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1715</v>
+        <v>0.1084</v>
       </c>
       <c r="J9" t="n">
-        <v>0.066</v>
+        <v>0.0641</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1238</v>
+        <v>0.0838</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08989999999999999</v>
+        <v>0.0725</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0882</v>
+        <v>0.0572</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bagging_GaussianNB</t>
+          <t>Bagging_SVC</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5626</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4491</v>
+        <v>0.4536</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3076</v>
+        <v>0.2384</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4103</v>
+        <v>0.3782</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3641</v>
+        <v>0.3075</v>
       </c>
       <c r="G10" t="n">
-        <v>0.531</v>
+        <v>0.5082</v>
       </c>
       <c r="H10" t="n">
-        <v>0.053</v>
+        <v>0.0747</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0961</v>
+        <v>0.1715</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0567</v>
+        <v>0.066</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0825</v>
+        <v>0.1238</v>
       </c>
       <c r="L10" t="n">
-        <v>0.06909999999999999</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0643</v>
+        <v>0.0882</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Bagging_DecisionTree</t>
+          <t>Bagging_GaussianNB</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.493</v>
+        <v>0.5626</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3796</v>
+        <v>0.4491</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3761</v>
+        <v>0.3076</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3763</v>
+        <v>0.4103</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3741</v>
+        <v>0.3641</v>
       </c>
       <c r="G11" t="n">
-        <v>0.472</v>
+        <v>0.531</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0422</v>
+        <v>0.053</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0559</v>
+        <v>0.0961</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0688</v>
+        <v>0.0567</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0482</v>
+        <v>0.0825</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0485</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0643</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Bagging_MLPClassifier</t>
+          <t>Bagging_DecisionTree</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5834</v>
+        <v>0.493</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4133</v>
+        <v>0.3796</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0772</v>
+        <v>0.3761</v>
       </c>
       <c r="E12" t="n">
-        <v>0.2169</v>
+        <v>0.3763</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1288</v>
+        <v>0.3741</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4839</v>
+        <v>0.472</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0142</v>
+        <v>0.0422</v>
       </c>
       <c r="I12" t="n">
-        <v>0.07480000000000001</v>
+        <v>0.0559</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0328</v>
+        <v>0.0688</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0688</v>
+        <v>0.0482</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0495</v>
+        <v>0.0485</v>
       </c>
       <c r="M12" t="n">
-        <v>0.07340000000000001</v>
+        <v>0.08599999999999999</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bagging_LogisticRegression</t>
+          <t>Bagging_MLPClassifier</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.5834</v>
       </c>
       <c r="C13" t="n">
-        <v>0.449</v>
+        <v>0.4133</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4964</v>
+        <v>0.0772</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4576</v>
+        <v>0.2169</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4713</v>
+        <v>0.1288</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5317</v>
+        <v>0.4839</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0988</v>
+        <v>0.0142</v>
       </c>
       <c r="I13" t="n">
-        <v>0.109</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1276</v>
+        <v>0.0328</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1119</v>
+        <v>0.0688</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1169</v>
+        <v>0.0495</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0934</v>
+        <v>0.07340000000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Bagging_TabPFN</t>
+          <t>Bagging_LogisticRegression</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5799</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3667</v>
+        <v>0.449</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0511</v>
+        <v>0.4964</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1561</v>
+        <v>0.4576</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.4713</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4878</v>
+        <v>0.5317</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0128</v>
+        <v>0.0988</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1944</v>
+        <v>0.109</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0319</v>
+        <v>0.1276</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0853</v>
+        <v>0.1119</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0518</v>
+        <v>0.1169</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0771</v>
+        <v>0.0934</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Voting_soft_DecisionTree+MLPClassifier+TabPFN</t>
+          <t>Bagging_TabPFN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5419</v>
+        <v>0.5799</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4129</v>
+        <v>0.3667</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3431</v>
+        <v>0.0511</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3935</v>
+        <v>0.1561</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3708</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4872</v>
+        <v>0.4878</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0463</v>
+        <v>0.0128</v>
       </c>
       <c r="I15" t="n">
-        <v>0.06469999999999999</v>
+        <v>0.1944</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1188</v>
+        <v>0.0319</v>
       </c>
       <c r="K15" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.0853</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0958</v>
+        <v>0.0518</v>
       </c>
       <c r="M15" t="n">
-        <v>0.06759999999999999</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Voting_soft_RandomForest+DecisionTree+MLPClassifier</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.5003</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.3844</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.4293</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.3907</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.4023</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.4694</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.0438</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.0579</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.1471</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0.0716</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.0955</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.06950000000000001</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Voting_soft_SVC+DecisionTree+MLPClassifier+TabPFN</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.5486</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.4078</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.2486</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.359</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.3063</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.4858</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.0291</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.0544</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.0595</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.0516</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.0544</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.0595</v>
+        <v>0.0771</v>
       </c>
     </row>
   </sheetData>
@@ -1211,7 +1125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1608,156 +1522,6 @@
       </c>
       <c r="G15" t="n">
         <v>0.5113</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Voting_hard_RandomForest+SVC+LogisticRegression+TabPFN</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>0.5934</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.5714</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.2051</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.4211</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.3019</v>
-      </c>
-      <c r="G16" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Voting_hard_RandomForest+SVC+DecisionTree+TabPFN</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>0.5495</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.4167</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.1282</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.2874</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.1961</v>
-      </c>
-      <c r="G17" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Voting_hard_RandomForest+SVC+GaussianNB+TabPFN</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>0.6044</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.1538</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G18" t="n">
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Voting_soft_DecisionTree+MLPClassifier+TabPFN</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>0.5054999999999999</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.2308</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.2857</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.4463</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Voting_soft_RandomForest+DecisionTree+MLPClassifier</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>0.4505</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.3659</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.3846</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.3695</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.4546</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Voting_soft_SVC+DecisionTree+MLPClassifier+TabPFN</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>0.5165</v>
-      </c>
-      <c r="C21" t="n">
-        <v>0.3529</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.1538</v>
-      </c>
-      <c r="E21" t="n">
-        <v>0.2804</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.2143</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.4463</v>
       </c>
     </row>
   </sheetData>
